--- a/ExcelConfigs/LevelConfig.xlsx
+++ b/ExcelConfigs/LevelConfig.xlsx
@@ -1,33 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="22188" windowHeight="9060"/>
+    <workbookView windowWidth="23028" windowHeight="9947"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="82">
   <si>
     <t>唯一标识</t>
   </si>
@@ -128,7 +115,7 @@
     <t>第二关</t>
   </si>
   <si>
-    <t>冰箱,智能垃圾桶,扫地机器人</t>
+    <t>冰箱,滚筒洗衣机,烧水壶</t>
   </si>
   <si>
     <t>3,1,5</t>
@@ -158,18 +145,18 @@
     <t>第三关</t>
   </si>
   <si>
-    <t>冰箱,智能垃圾桶,扫地机器人,滚筒洗衣机,烧水壶</t>
+    <t>冰箱,滚筒洗衣机,烧水壶,智能垃圾桶,扫地机器人</t>
   </si>
   <si>
     <t>5,1,4,2,3</t>
   </si>
   <si>
-    <t>3,3,3,3,3</t>
-  </si>
-  <si>
     <t>4,4,4,4,4</t>
   </si>
   <si>
+    <t>6,6,6,6,6</t>
+  </si>
+  <si>
     <t>0,0,0,0,0</t>
   </si>
   <si>
@@ -188,18 +175,18 @@
     <t>第四关</t>
   </si>
   <si>
-    <t>冰箱,智能垃圾桶,扫地机器人,滚筒洗衣机,烧水壶,空调</t>
+    <t>冰箱,滚筒洗衣机,烧水壶,智能垃圾桶,扫地机器人,空调</t>
   </si>
   <si>
     <t>5,1,5,2,3,4</t>
   </si>
   <si>
-    <t>3,3,3,3,3,3</t>
-  </si>
-  <si>
     <t>4,4,4,4,4,4</t>
   </si>
   <si>
+    <t>6,6,6,6,6,6</t>
+  </si>
+  <si>
     <t>0,0,0,0,0,0</t>
   </si>
   <si>
@@ -218,7 +205,7 @@
     <t>第五关</t>
   </si>
   <si>
-    <t>冰箱,智能垃圾桶,扫地机器人,滚筒洗衣机,烧水壶,空调,时钟</t>
+    <t>冰箱,滚筒洗衣机,烧水壶,智能垃圾桶,扫地机器人,空调,时钟</t>
   </si>
   <si>
     <t>4,3,2,1,5,3,6</t>
@@ -227,7 +214,7 @@
     <t>3,3,3,3,3,3,4</t>
   </si>
   <si>
-    <t>3,3,3,3,3,3,5</t>
+    <t>6,6,6,6,6,6,6</t>
   </si>
   <si>
     <t>0,0,0,0,0,0,0</t>
@@ -236,7 +223,7 @@
     <t>0.07,0.07,0.07,0.07,0.07,0.07,0.07</t>
   </si>
   <si>
-    <t>60,60,60,60,60,60,60</t>
+    <t>50,50,50,50,50,50，50</t>
   </si>
   <si>
     <t>100,100,100,100,100,100,100</t>
@@ -251,6 +238,9 @@
     <t>2,3,4,1,5,3,6</t>
   </si>
   <si>
+    <t>5,5,5,5,5,5,5</t>
+  </si>
+  <si>
     <t>空调最害怕的是蟑螂，千万不要让蟑螂钻进空调！</t>
   </si>
   <si>
@@ -263,7 +253,7 @@
     <t>3,3,3,3,3,3,3</t>
   </si>
   <si>
-    <t>0.06,0.06,0.06,0.06,0.06,0.06,0.06</t>
+    <t>4,4,4,4,4,4,4</t>
   </si>
   <si>
     <t>90,90,90,90,90,90,90</t>
@@ -275,12 +265,12 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="21">
     <font>
@@ -295,6 +285,103 @@
       <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <u/>
@@ -305,6 +392,22 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <u/>
       <sz val="11"/>
       <color rgb="FF800080"/>
@@ -313,91 +416,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="11"/>
       <color theme="1"/>
@@ -407,35 +425,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FFFA7D00"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -450,6 +440,102 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -462,7 +548,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -474,37 +590,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -516,121 +614,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -641,6 +631,45 @@
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -663,46 +692,7 @@
       <right/>
       <top/>
       <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
         <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -724,15 +714,6 @@
     <border>
       <left/>
       <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
       <top style="thin">
         <color theme="4"/>
       </top>
@@ -741,153 +722,162 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="19" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="26" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -910,52 +900,52 @@
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
-    <cellStyle name="货币" xfId="2" builtinId="4"/>
-    <cellStyle name="百分比" xfId="3" builtinId="5"/>
-    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
-    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
-    <cellStyle name="超链接" xfId="6" builtinId="8"/>
-    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
-    <cellStyle name="注释" xfId="8" builtinId="10"/>
-    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
-    <cellStyle name="标题" xfId="10" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
-    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="货币[0]" xfId="1" builtinId="7"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="2" builtinId="38"/>
+    <cellStyle name="输入" xfId="3" builtinId="20"/>
+    <cellStyle name="货币" xfId="4" builtinId="4"/>
+    <cellStyle name="千位分隔[0]" xfId="5" builtinId="6"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="6" builtinId="39"/>
+    <cellStyle name="差" xfId="7" builtinId="27"/>
+    <cellStyle name="千位分隔" xfId="8" builtinId="3"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="9" builtinId="40"/>
+    <cellStyle name="超链接" xfId="10" builtinId="8"/>
+    <cellStyle name="百分比" xfId="11" builtinId="5"/>
+    <cellStyle name="已访问的超链接" xfId="12" builtinId="9"/>
+    <cellStyle name="注释" xfId="13" builtinId="10"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="14" builtinId="36"/>
     <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="输入" xfId="16" builtinId="20"/>
-    <cellStyle name="输出" xfId="17" builtinId="21"/>
-    <cellStyle name="计算" xfId="18" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
-    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
-    <cellStyle name="汇总" xfId="21" builtinId="25"/>
-    <cellStyle name="好" xfId="22" builtinId="26"/>
-    <cellStyle name="差" xfId="23" builtinId="27"/>
-    <cellStyle name="适中" xfId="24" builtinId="28"/>
-    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
-    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
-    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
-    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
-    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="警告文本" xfId="16" builtinId="11"/>
+    <cellStyle name="标题" xfId="17" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="18" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="19" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="20" builtinId="17"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="21" builtinId="32"/>
+    <cellStyle name="标题 3" xfId="22" builtinId="18"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="23" builtinId="44"/>
+    <cellStyle name="输出" xfId="24" builtinId="21"/>
+    <cellStyle name="计算" xfId="25" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="26" builtinId="23"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="27" builtinId="50"/>
+    <cellStyle name="强调文字颜色 2" xfId="28" builtinId="33"/>
+    <cellStyle name="链接单元格" xfId="29" builtinId="24"/>
+    <cellStyle name="汇总" xfId="30" builtinId="25"/>
+    <cellStyle name="好" xfId="31" builtinId="26"/>
+    <cellStyle name="适中" xfId="32" builtinId="28"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="33" builtinId="46"/>
+    <cellStyle name="强调文字颜色 1" xfId="34" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="35" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="36" builtinId="31"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="37" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="38" builtinId="35"/>
+    <cellStyle name="强调文字颜色 3" xfId="39" builtinId="37"/>
+    <cellStyle name="强调文字颜色 4" xfId="40" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="41" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="42" builtinId="43"/>
+    <cellStyle name="强调文字颜色 5" xfId="43" builtinId="45"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="44" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="45" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="46" builtinId="49"/>
     <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
     <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
@@ -1564,7 +1554,7 @@
         <v>65</v>
       </c>
       <c r="G9" t="s">
-        <v>66</v>
+        <v>74</v>
       </c>
       <c r="H9" t="s">
         <v>67</v>
@@ -1579,7 +1569,7 @@
         <v>70</v>
       </c>
       <c r="L9" s="2" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="10" spans="1:12">
@@ -1587,7 +1577,7 @@
         <v>7</v>
       </c>
       <c r="B10" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C10">
         <v>105</v>
@@ -1596,28 +1586,28 @@
         <v>63</v>
       </c>
       <c r="E10" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F10" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G10" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="H10" t="s">
         <v>67</v>
       </c>
       <c r="I10" t="s">
-        <v>78</v>
+        <v>68</v>
       </c>
       <c r="J10" t="s">
         <v>69</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="L10" s="2" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
   </sheetData>

--- a/ExcelConfigs/LevelConfig.xlsx
+++ b/ExcelConfigs/LevelConfig.xlsx
@@ -1,15 +1,28 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="23028" windowHeight="9947"/>
+    <workbookView windowWidth="17111" windowHeight="8460"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="144525"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -223,7 +236,7 @@
     <t>0.07,0.07,0.07,0.07,0.07,0.07,0.07</t>
   </si>
   <si>
-    <t>50,50,50,50,50,50，50</t>
+    <t>50,50,50,50,50,50,50</t>
   </si>
   <si>
     <t>100,100,100,100,100,100,100</t>
@@ -265,12 +278,12 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
   <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
   </numFmts>
   <fonts count="21">
     <font>
@@ -287,15 +300,71 @@
       <charset val="134"/>
     </font>
     <font>
+      <u/>
       <sz val="11"/>
-      <color theme="0"/>
+      <color rgb="FF0000FF"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF800080"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -310,83 +379,8 @@
     </font>
     <font>
       <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -400,17 +394,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
       <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
+      <color rgb="FFFA7D00"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -425,7 +410,35 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF006100"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -440,31 +453,175 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
+        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -476,151 +633,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -631,45 +644,6 @@
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -692,7 +666,46 @@
       <right/>
       <top/>
       <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
         <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -714,6 +727,15 @@
     <border>
       <left/>
       <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
       <top style="thin">
         <color theme="4"/>
       </top>
@@ -722,162 +744,153 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="19" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="18" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="26" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -900,52 +913,52 @@
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="货币[0]" xfId="1" builtinId="7"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="2" builtinId="38"/>
-    <cellStyle name="输入" xfId="3" builtinId="20"/>
-    <cellStyle name="货币" xfId="4" builtinId="4"/>
-    <cellStyle name="千位分隔[0]" xfId="5" builtinId="6"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="6" builtinId="39"/>
-    <cellStyle name="差" xfId="7" builtinId="27"/>
-    <cellStyle name="千位分隔" xfId="8" builtinId="3"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="9" builtinId="40"/>
-    <cellStyle name="超链接" xfId="10" builtinId="8"/>
-    <cellStyle name="百分比" xfId="11" builtinId="5"/>
-    <cellStyle name="已访问的超链接" xfId="12" builtinId="9"/>
-    <cellStyle name="注释" xfId="13" builtinId="10"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="14" builtinId="36"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
     <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="警告文本" xfId="16" builtinId="11"/>
-    <cellStyle name="标题" xfId="17" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="18" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="19" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="20" builtinId="17"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="21" builtinId="32"/>
-    <cellStyle name="标题 3" xfId="22" builtinId="18"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="23" builtinId="44"/>
-    <cellStyle name="输出" xfId="24" builtinId="21"/>
-    <cellStyle name="计算" xfId="25" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="26" builtinId="23"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="27" builtinId="50"/>
-    <cellStyle name="强调文字颜色 2" xfId="28" builtinId="33"/>
-    <cellStyle name="链接单元格" xfId="29" builtinId="24"/>
-    <cellStyle name="汇总" xfId="30" builtinId="25"/>
-    <cellStyle name="好" xfId="31" builtinId="26"/>
-    <cellStyle name="适中" xfId="32" builtinId="28"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="33" builtinId="46"/>
-    <cellStyle name="强调文字颜色 1" xfId="34" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="35" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="36" builtinId="31"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="37" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="38" builtinId="35"/>
-    <cellStyle name="强调文字颜色 3" xfId="39" builtinId="37"/>
-    <cellStyle name="强调文字颜色 4" xfId="40" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="41" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="42" builtinId="43"/>
-    <cellStyle name="强调文字颜色 5" xfId="43" builtinId="45"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="44" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="45" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="46" builtinId="49"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
     <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
     <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>

--- a/ExcelConfigs/LevelConfig.xlsx
+++ b/ExcelConfigs/LevelConfig.xlsx
@@ -1,33 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="17111" windowHeight="8460"/>
+    <workbookView windowWidth="23028" windowHeight="9947"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="85">
   <si>
     <t>唯一标识</t>
   </si>
@@ -122,6 +109,9 @@
     <t>冰箱</t>
   </si>
   <si>
+    <t>100</t>
+  </si>
+  <si>
     <t>冰箱先生喜欢讲冷笑话，更喜欢有人听他讲冷笑话</t>
   </si>
   <si>
@@ -164,22 +154,22 @@
     <t>5,1,4,2,3</t>
   </si>
   <si>
-    <t>4,4,4,4,4</t>
-  </si>
-  <si>
-    <t>6,6,6,6,6</t>
+    <t>5,5,5,5,5</t>
+  </si>
+  <si>
+    <t>8,8,8,8,8</t>
   </si>
   <si>
     <t>0,0,0,0,0</t>
   </si>
   <si>
-    <t>0.08,0.08,0.08,0.08,0.08</t>
-  </si>
-  <si>
-    <t>50,50,50,50,50</t>
-  </si>
-  <si>
-    <t>100,100,100,100,100</t>
+    <t>0.1,0.1,0.1,0.1,0.1</t>
+  </si>
+  <si>
+    <t>60,60,60,60,60</t>
+  </si>
+  <si>
+    <t>120,120,120,120,120,120</t>
   </si>
   <si>
     <t>扫地机器人喜欢捉迷藏，没有人来找的话，会失望的吧</t>
@@ -194,22 +184,22 @@
     <t>5,1,5,2,3,4</t>
   </si>
   <si>
-    <t>4,4,4,4,4,4</t>
-  </si>
-  <si>
-    <t>6,6,6,6,6,6</t>
+    <t>5,5,5,5,5,5</t>
+  </si>
+  <si>
+    <t>7,7,7,7,7,7</t>
   </si>
   <si>
     <t>0,0,0,0,0,0</t>
   </si>
   <si>
-    <t>0.08,0.08,0.08,0.08,0.08,0.08</t>
-  </si>
-  <si>
-    <t>50,50,50,50,50,50</t>
-  </si>
-  <si>
-    <t>100,100,100,100,100,100</t>
+    <t>0.1,0.1,0.1,0.1,0.1,0.1</t>
+  </si>
+  <si>
+    <t>75,75,75,75,75,75</t>
+  </si>
+  <si>
+    <t>150,150,150,150,150,150</t>
   </si>
   <si>
     <t>滚筒洗衣机容易焦虑，疯狂内耗时，记得安慰一下</t>
@@ -224,52 +214,58 @@
     <t>4,3,2,1,5,3,6</t>
   </si>
   <si>
-    <t>3,3,3,3,3,3,4</t>
-  </si>
-  <si>
-    <t>6,6,6,6,6,6,6</t>
+    <t>5,5,5,5,5,5,10</t>
+  </si>
+  <si>
+    <t>6,6,6,6,6,6,15</t>
   </si>
   <si>
     <t>0,0,0,0,0,0,0</t>
   </si>
   <si>
+    <t>0.08,0.08,0.08,0.08,0.08,0.08,0.08</t>
+  </si>
+  <si>
+    <t>100,100,100,100,100,100,100</t>
+  </si>
+  <si>
+    <t>200,200,200,200,200,200,200</t>
+  </si>
+  <si>
+    <t>烧水壶喜欢发呆，有时忘了自己的工作，记得提醒一下</t>
+  </si>
+  <si>
+    <t>第六关</t>
+  </si>
+  <si>
+    <t>2,3,4,1,5,3,10</t>
+  </si>
+  <si>
+    <t>4,4,4,4,4,4,8</t>
+  </si>
+  <si>
+    <t>5,5,5,5,5,5,12</t>
+  </si>
+  <si>
+    <t>空调最害怕的是蟑螂，千万不要让蟑螂钻进空调！</t>
+  </si>
+  <si>
+    <t>第七关</t>
+  </si>
+  <si>
+    <t>2,1,2,1,4,3,7</t>
+  </si>
+  <si>
+    <t>2,2,2,2,2,2,6</t>
+  </si>
+  <si>
+    <t>6,6,6,6,6,6,8</t>
+  </si>
+  <si>
     <t>0.07,0.07,0.07,0.07,0.07,0.07,0.07</t>
   </si>
   <si>
-    <t>50,50,50,50,50,50,50</t>
-  </si>
-  <si>
-    <t>100,100,100,100,100,100,100</t>
-  </si>
-  <si>
-    <t>烧水壶喜欢发呆，有时忘了自己的工作，记得提醒一下</t>
-  </si>
-  <si>
-    <t>第六关</t>
-  </si>
-  <si>
-    <t>2,3,4,1,5,3,6</t>
-  </si>
-  <si>
-    <t>5,5,5,5,5,5,5</t>
-  </si>
-  <si>
-    <t>空调最害怕的是蟑螂，千万不要让蟑螂钻进空调！</t>
-  </si>
-  <si>
-    <t>第七关</t>
-  </si>
-  <si>
-    <t>2,1,2,1,4,3,3</t>
-  </si>
-  <si>
-    <t>3,3,3,3,3,3,3</t>
-  </si>
-  <si>
-    <t>4,4,4,4,4,4,4</t>
-  </si>
-  <si>
-    <t>90,90,90,90,90,90,90</t>
+    <t>180,180,180,180,180,180,180</t>
   </si>
   <si>
     <t>时钟是个急性子，没人盯着的话，他会偷偷快跑</t>
@@ -278,12 +274,12 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="21">
     <font>
@@ -298,6 +294,89 @@
       <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <u/>
@@ -308,32 +387,16 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF800080"/>
+      <color rgb="FF3F3F3F"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <color rgb="FFFA7D00"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -348,31 +411,15 @@
     </font>
     <font>
       <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color rgb="FF006100"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -386,63 +433,12 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color rgb="FF9C6500"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
   <fills count="33">
     <fill>
@@ -453,19 +449,139 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -477,163 +593,43 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -647,35 +643,11 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right/>
       <top/>
       <bottom style="medium">
         <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -695,6 +667,26 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
         <color rgb="FF3F3F3F"/>
       </left>
@@ -706,6 +698,30 @@
       </top>
       <bottom style="thin">
         <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
       </bottom>
       <diagonal/>
     </border>
@@ -724,177 +740,157 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="10" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="22" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="17" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="25" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -907,58 +903,64 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
-    <cellStyle name="货币" xfId="2" builtinId="4"/>
-    <cellStyle name="百分比" xfId="3" builtinId="5"/>
-    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
-    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
-    <cellStyle name="超链接" xfId="6" builtinId="8"/>
-    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
-    <cellStyle name="注释" xfId="8" builtinId="10"/>
-    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
-    <cellStyle name="标题" xfId="10" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
-    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="货币[0]" xfId="1" builtinId="7"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="2" builtinId="38"/>
+    <cellStyle name="输入" xfId="3" builtinId="20"/>
+    <cellStyle name="货币" xfId="4" builtinId="4"/>
+    <cellStyle name="千位分隔[0]" xfId="5" builtinId="6"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="6" builtinId="39"/>
+    <cellStyle name="差" xfId="7" builtinId="27"/>
+    <cellStyle name="千位分隔" xfId="8" builtinId="3"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="9" builtinId="40"/>
+    <cellStyle name="超链接" xfId="10" builtinId="8"/>
+    <cellStyle name="百分比" xfId="11" builtinId="5"/>
+    <cellStyle name="已访问的超链接" xfId="12" builtinId="9"/>
+    <cellStyle name="注释" xfId="13" builtinId="10"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="14" builtinId="36"/>
     <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="输入" xfId="16" builtinId="20"/>
-    <cellStyle name="输出" xfId="17" builtinId="21"/>
-    <cellStyle name="计算" xfId="18" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
-    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
-    <cellStyle name="汇总" xfId="21" builtinId="25"/>
-    <cellStyle name="好" xfId="22" builtinId="26"/>
-    <cellStyle name="差" xfId="23" builtinId="27"/>
-    <cellStyle name="适中" xfId="24" builtinId="28"/>
-    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
-    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
-    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
-    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
-    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="警告文本" xfId="16" builtinId="11"/>
+    <cellStyle name="标题" xfId="17" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="18" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="19" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="20" builtinId="17"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="21" builtinId="32"/>
+    <cellStyle name="标题 3" xfId="22" builtinId="18"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="23" builtinId="44"/>
+    <cellStyle name="输出" xfId="24" builtinId="21"/>
+    <cellStyle name="计算" xfId="25" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="26" builtinId="23"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="27" builtinId="50"/>
+    <cellStyle name="强调文字颜色 2" xfId="28" builtinId="33"/>
+    <cellStyle name="链接单元格" xfId="29" builtinId="24"/>
+    <cellStyle name="汇总" xfId="30" builtinId="25"/>
+    <cellStyle name="好" xfId="31" builtinId="26"/>
+    <cellStyle name="适中" xfId="32" builtinId="28"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="33" builtinId="46"/>
+    <cellStyle name="强调文字颜色 1" xfId="34" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="35" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="36" builtinId="31"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="37" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="38" builtinId="35"/>
+    <cellStyle name="强调文字颜色 3" xfId="39" builtinId="37"/>
+    <cellStyle name="强调文字颜色 4" xfId="40" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="41" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="42" builtinId="43"/>
+    <cellStyle name="强调文字颜色 5" xfId="43" builtinId="45"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="44" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="45" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="46" builtinId="49"/>
     <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
     <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
@@ -1274,10 +1276,10 @@
       <c r="J1" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="4" t="s">
+      <c r="K1" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="2" t="s">
+      <c r="L1" s="4" t="s">
         <v>11</v>
       </c>
     </row>
@@ -1297,25 +1299,25 @@
       <c r="E2" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="F2" t="s">
+      <c r="F2" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="G2" t="s">
+      <c r="G2" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="H2" t="s">
+      <c r="H2" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="I2" t="s">
+      <c r="I2" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="J2" t="s">
+      <c r="J2" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="K2" s="1" t="s">
+      <c r="K2" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="L2" s="2" t="s">
+      <c r="L2" s="4" t="s">
         <v>23</v>
       </c>
     </row>
@@ -1335,292 +1337,292 @@
       <c r="E3" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="F3" t="s">
+      <c r="F3" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="G3" t="s">
+      <c r="G3" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="H3" t="s">
+      <c r="H3" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="I3" t="s">
+      <c r="I3" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="J3" t="s">
+      <c r="J3" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="K3" s="1" t="s">
+      <c r="K3" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="L3" s="2" t="s">
+      <c r="L3" s="4" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="4" spans="1:12">
-      <c r="A4">
+      <c r="A4" s="4">
         <v>1</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="C4">
+      <c r="C4" s="4">
         <v>30</v>
       </c>
-      <c r="D4" t="s">
+      <c r="D4" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="E4">
+      <c r="E4" s="4">
         <v>1</v>
       </c>
-      <c r="F4">
+      <c r="F4" s="4">
         <v>2</v>
       </c>
-      <c r="G4">
+      <c r="G4" s="4">
         <v>2</v>
       </c>
-      <c r="H4">
+      <c r="H4" s="4">
         <v>0</v>
       </c>
-      <c r="I4">
+      <c r="I4" s="4">
         <v>0.05</v>
       </c>
-      <c r="J4">
+      <c r="J4" s="4">
         <v>50</v>
       </c>
-      <c r="K4" s="1">
-        <v>100</v>
-      </c>
-      <c r="L4" s="2" t="s">
+      <c r="K4" s="6" t="s">
         <v>31</v>
+      </c>
+      <c r="L4" s="4" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="5" spans="1:12">
-      <c r="A5">
+      <c r="A5" s="4">
         <v>2</v>
       </c>
-      <c r="B5" t="s">
-        <v>32</v>
-      </c>
-      <c r="C5">
+      <c r="B5" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="C5" s="4">
         <v>60</v>
       </c>
-      <c r="D5" t="s">
-        <v>33</v>
-      </c>
-      <c r="E5" t="s">
+      <c r="D5" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="F5" t="s">
+      <c r="E5" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="G5" t="s">
+      <c r="F5" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="H5" t="s">
+      <c r="G5" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="I5" t="s">
+      <c r="H5" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="J5" t="s">
+      <c r="I5" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="K5" s="1" t="s">
+      <c r="J5" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="L5" s="2" t="s">
+      <c r="K5" s="6" t="s">
         <v>41</v>
+      </c>
+      <c r="L5" s="4" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="6" spans="1:12">
-      <c r="A6">
+      <c r="A6" s="4">
         <v>3</v>
       </c>
-      <c r="B6" t="s">
-        <v>42</v>
-      </c>
-      <c r="C6">
+      <c r="B6" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="C6" s="4">
         <v>75</v>
       </c>
-      <c r="D6" t="s">
-        <v>43</v>
-      </c>
-      <c r="E6" t="s">
+      <c r="D6" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="F6" t="s">
+      <c r="E6" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="G6" t="s">
+      <c r="F6" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="H6" t="s">
+      <c r="G6" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="I6" t="s">
+      <c r="H6" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="J6" t="s">
+      <c r="I6" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="K6" t="s">
+      <c r="J6" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="L6" s="2" t="s">
+      <c r="K6" s="6" t="s">
         <v>51</v>
+      </c>
+      <c r="L6" s="4" t="s">
+        <v>52</v>
       </c>
     </row>
     <row r="7" spans="1:12">
-      <c r="A7">
+      <c r="A7" s="4">
         <v>4</v>
       </c>
-      <c r="B7" t="s">
-        <v>52</v>
-      </c>
-      <c r="C7">
+      <c r="B7" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="C7" s="4">
         <v>90</v>
       </c>
-      <c r="D7" t="s">
-        <v>53</v>
-      </c>
-      <c r="E7" t="s">
+      <c r="D7" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="F7" t="s">
+      <c r="E7" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="G7" t="s">
+      <c r="F7" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="H7" t="s">
+      <c r="G7" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="I7" t="s">
+      <c r="H7" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="J7" t="s">
+      <c r="I7" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="K7" s="1" t="s">
+      <c r="J7" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="L7" s="2" t="s">
+      <c r="K7" s="6" t="s">
         <v>61</v>
+      </c>
+      <c r="L7" s="4" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="8" spans="1:12">
-      <c r="A8">
+      <c r="A8" s="4">
         <v>5</v>
       </c>
-      <c r="B8" t="s">
-        <v>62</v>
-      </c>
-      <c r="C8">
+      <c r="B8" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="C8" s="4">
         <v>90</v>
       </c>
-      <c r="D8" t="s">
-        <v>63</v>
-      </c>
-      <c r="E8" t="s">
+      <c r="D8" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="F8" t="s">
+      <c r="E8" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="G8" t="s">
+      <c r="F8" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="H8" t="s">
+      <c r="G8" s="4" t="s">
         <v>67</v>
       </c>
-      <c r="I8" t="s">
+      <c r="H8" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="J8" t="s">
+      <c r="I8" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="K8" s="1" t="s">
+      <c r="J8" s="6" t="s">
         <v>70</v>
       </c>
-      <c r="L8" s="2" t="s">
+      <c r="K8" s="6" t="s">
         <v>71</v>
+      </c>
+      <c r="L8" s="4" t="s">
+        <v>72</v>
       </c>
     </row>
     <row r="9" spans="1:12">
-      <c r="A9">
+      <c r="A9" s="4">
         <v>6</v>
       </c>
-      <c r="B9" t="s">
-        <v>72</v>
-      </c>
-      <c r="C9">
+      <c r="B9" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="C9" s="4">
         <v>105</v>
       </c>
-      <c r="D9" t="s">
-        <v>63</v>
-      </c>
-      <c r="E9" t="s">
-        <v>73</v>
-      </c>
-      <c r="F9" t="s">
-        <v>65</v>
-      </c>
-      <c r="G9" t="s">
+      <c r="D9" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="E9" s="4" t="s">
         <v>74</v>
       </c>
-      <c r="H9" t="s">
-        <v>67</v>
-      </c>
-      <c r="I9" t="s">
+      <c r="F9" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="G9" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="H9" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="J9" t="s">
+      <c r="I9" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="K9" s="1" t="s">
+      <c r="J9" s="6" t="s">
         <v>70</v>
       </c>
-      <c r="L9" s="2" t="s">
-        <v>75</v>
+      <c r="K9" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="L9" s="4" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="10" spans="1:12">
-      <c r="A10">
+      <c r="A10" s="4">
         <v>7</v>
       </c>
-      <c r="B10" t="s">
-        <v>76</v>
-      </c>
-      <c r="C10">
-        <v>105</v>
-      </c>
-      <c r="D10" t="s">
-        <v>63</v>
-      </c>
-      <c r="E10" t="s">
-        <v>77</v>
-      </c>
-      <c r="F10" t="s">
+      <c r="B10" s="4" t="s">
         <v>78</v>
       </c>
-      <c r="G10" t="s">
+      <c r="C10" s="4">
+        <v>120</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="E10" s="4" t="s">
         <v>79</v>
       </c>
-      <c r="H10" t="s">
-        <v>67</v>
-      </c>
-      <c r="I10" t="s">
+      <c r="F10" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="G10" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="H10" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="J10" t="s">
-        <v>69</v>
-      </c>
-      <c r="K10" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="L10" s="2" t="s">
-        <v>81</v>
+      <c r="I10" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="J10" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="K10" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="L10" s="4" t="s">
+        <v>84</v>
       </c>
     </row>
   </sheetData>
